--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_008.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_008.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="152">
   <si>
     <t>Sezione</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>evento.intestatari[0]</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Atto nascita intestatario</t>
@@ -520,11 +526,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="45.05859375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
@@ -3409,53 +3415,53 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="C126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E127" s="2" t="s">
+      <c r="F127" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G127" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>104</v>
@@ -3464,7 +3470,7 @@
         <v>12</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>105</v>
@@ -3473,12 +3479,12 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>106</v>
@@ -3487,7 +3493,7 @@
         <v>12</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>107</v>
@@ -3496,12 +3502,12 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>108</v>
@@ -3510,7 +3516,7 @@
         <v>12</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>109</v>
@@ -3519,12 +3525,12 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>110</v>
@@ -3533,44 +3539,44 @@
         <v>12</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>113</v>
@@ -3579,44 +3585,44 @@
         <v>12</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>116</v>
@@ -3625,7 +3631,7 @@
         <v>12</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>117</v>
@@ -3634,12 +3640,12 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>118</v>
@@ -3648,7 +3654,7 @@
         <v>12</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>119</v>
@@ -3657,12 +3663,12 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>120</v>
@@ -3671,7 +3677,7 @@
         <v>12</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>121</v>
@@ -3680,44 +3686,44 @@
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>127</v>
@@ -3731,7 +3737,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>128</v>
@@ -3740,7 +3746,7 @@
         <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>129</v>
@@ -3754,19 +3760,19 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
@@ -3777,16 +3783,16 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>132</v>
@@ -3800,16 +3806,16 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>134</v>
@@ -3823,7 +3829,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>135</v>
@@ -3832,7 +3838,7 @@
         <v>12</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>136</v>
@@ -3846,19 +3852,19 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="C145" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E145" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>10</v>
@@ -3869,16 +3875,16 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>142</v>
@@ -3892,7 +3898,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>143</v>
@@ -3901,7 +3907,7 @@
         <v>9</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>144</v>
@@ -3915,19 +3921,19 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="C148" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>10</v>
@@ -3938,16 +3944,16 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>149</v>
@@ -3956,6 +3962,29 @@
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" s="2" t="s">
         <v>20</v>
       </c>
     </row>
